--- a/downloads/labs.xlsx
+++ b/downloads/labs.xlsx
@@ -547,7 +547,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L790"/>
+  <dimension ref="A1:L792"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -36898,14 +36898,14 @@
       </c>
       <c r="E725" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="F725" t="n">
-        <v>220</v>
+        <v>211.86</v>
       </c>
       <c r="G725" t="n">
-        <v>259.6</v>
+        <v>250</v>
       </c>
       <c r="H725">
         <f>הגדרות!B6</f>
@@ -36946,14 +36946,14 @@
       </c>
       <c r="E726" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="F726" t="n">
+        <v>237.29</v>
+      </c>
+      <c r="G726" t="n">
         <v>280</v>
-      </c>
-      <c r="G726" t="n">
-        <v>330.4</v>
       </c>
       <c r="H726">
         <f>הגדרות!B6</f>
@@ -36994,14 +36994,14 @@
       </c>
       <c r="E727" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="F727" t="n">
+        <v>237.29</v>
+      </c>
+      <c r="G727" t="n">
         <v>280</v>
-      </c>
-      <c r="G727" t="n">
-        <v>330.4</v>
       </c>
       <c r="H727">
         <f>הגדרות!B6</f>
@@ -37042,14 +37042,14 @@
       </c>
       <c r="E728" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="F728" t="n">
+        <v>237.29</v>
+      </c>
+      <c r="G728" t="n">
         <v>280</v>
-      </c>
-      <c r="G728" t="n">
-        <v>330.4</v>
       </c>
       <c r="H728">
         <f>הגדרות!B6</f>
@@ -37090,14 +37090,14 @@
       </c>
       <c r="E729" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="F729" t="n">
+        <v>237.29</v>
+      </c>
+      <c r="G729" t="n">
         <v>280</v>
-      </c>
-      <c r="G729" t="n">
-        <v>330.4</v>
       </c>
       <c r="H729">
         <f>הגדרות!B6</f>
@@ -37138,14 +37138,14 @@
       </c>
       <c r="E730" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="F730" t="n">
+        <v>237.29</v>
+      </c>
+      <c r="G730" t="n">
         <v>280</v>
-      </c>
-      <c r="G730" t="n">
-        <v>330.4</v>
       </c>
       <c r="H730">
         <f>הגדרות!B6</f>
@@ -37186,14 +37186,14 @@
       </c>
       <c r="E731" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="F731" t="n">
+        <v>237.29</v>
+      </c>
+      <c r="G731" t="n">
         <v>280</v>
-      </c>
-      <c r="G731" t="n">
-        <v>330.4</v>
       </c>
       <c r="H731">
         <f>הגדרות!B6</f>
@@ -37234,14 +37234,14 @@
       </c>
       <c r="E732" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="F732" t="n">
+        <v>237.29</v>
+      </c>
+      <c r="G732" t="n">
         <v>280</v>
-      </c>
-      <c r="G732" t="n">
-        <v>330.4</v>
       </c>
       <c r="H732">
         <f>הגדרות!B6</f>
@@ -37282,14 +37282,14 @@
       </c>
       <c r="E733" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="F733" t="n">
+        <v>237.29</v>
+      </c>
+      <c r="G733" t="n">
         <v>280</v>
-      </c>
-      <c r="G733" t="n">
-        <v>330.4</v>
       </c>
       <c r="H733">
         <f>הגדרות!B6</f>
@@ -37330,14 +37330,14 @@
       </c>
       <c r="E734" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="F734" t="n">
+        <v>237.29</v>
+      </c>
+      <c r="G734" t="n">
         <v>280</v>
-      </c>
-      <c r="G734" t="n">
-        <v>330.4</v>
       </c>
       <c r="H734">
         <f>הגדרות!B6</f>
@@ -37378,14 +37378,14 @@
       </c>
       <c r="E735" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="F735" t="n">
+        <v>237.29</v>
+      </c>
+      <c r="G735" t="n">
         <v>280</v>
-      </c>
-      <c r="G735" t="n">
-        <v>330.4</v>
       </c>
       <c r="H735">
         <f>הגדרות!B6</f>
@@ -37426,14 +37426,14 @@
       </c>
       <c r="E736" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="F736" t="n">
+        <v>237.29</v>
+      </c>
+      <c r="G736" t="n">
         <v>280</v>
-      </c>
-      <c r="G736" t="n">
-        <v>330.4</v>
       </c>
       <c r="H736">
         <f>הגדרות!B6</f>
@@ -37474,14 +37474,14 @@
       </c>
       <c r="E737" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="F737" t="n">
+        <v>237.29</v>
+      </c>
+      <c r="G737" t="n">
         <v>280</v>
-      </c>
-      <c r="G737" t="n">
-        <v>330.4</v>
       </c>
       <c r="H737">
         <f>הגדרות!B6</f>
@@ -37522,14 +37522,14 @@
       </c>
       <c r="E738" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="F738" t="n">
+        <v>237.29</v>
+      </c>
+      <c r="G738" t="n">
         <v>280</v>
-      </c>
-      <c r="G738" t="n">
-        <v>330.4</v>
       </c>
       <c r="H738">
         <f>הגדרות!B6</f>
@@ -37570,14 +37570,14 @@
       </c>
       <c r="E739" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="F739" t="n">
+        <v>237.29</v>
+      </c>
+      <c r="G739" t="n">
         <v>280</v>
-      </c>
-      <c r="G739" t="n">
-        <v>330.4</v>
       </c>
       <c r="H739">
         <f>הגדרות!B6</f>
@@ -37618,14 +37618,14 @@
       </c>
       <c r="E740" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="F740" t="n">
+        <v>237.29</v>
+      </c>
+      <c r="G740" t="n">
         <v>280</v>
-      </c>
-      <c r="G740" t="n">
-        <v>330.4</v>
       </c>
       <c r="H740">
         <f>הגדרות!B6</f>
@@ -37666,14 +37666,14 @@
       </c>
       <c r="E741" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="F741" t="n">
+        <v>237.29</v>
+      </c>
+      <c r="G741" t="n">
         <v>280</v>
-      </c>
-      <c r="G741" t="n">
-        <v>330.4</v>
       </c>
       <c r="H741">
         <f>הגדרות!B6</f>
@@ -37714,14 +37714,14 @@
       </c>
       <c r="E742" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="F742" t="n">
+        <v>237.29</v>
+      </c>
+      <c r="G742" t="n">
         <v>280</v>
-      </c>
-      <c r="G742" t="n">
-        <v>330.4</v>
       </c>
       <c r="H742">
         <f>הגדרות!B6</f>
@@ -37762,14 +37762,14 @@
       </c>
       <c r="E743" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="F743" t="n">
+        <v>237.29</v>
+      </c>
+      <c r="G743" t="n">
         <v>280</v>
-      </c>
-      <c r="G743" t="n">
-        <v>330.4</v>
       </c>
       <c r="H743">
         <f>הגדרות!B6</f>
@@ -37810,14 +37810,14 @@
       </c>
       <c r="E744" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="F744" t="n">
+        <v>237.29</v>
+      </c>
+      <c r="G744" t="n">
         <v>280</v>
-      </c>
-      <c r="G744" t="n">
-        <v>330.4</v>
       </c>
       <c r="H744">
         <f>הגדרות!B6</f>
@@ -37858,14 +37858,14 @@
       </c>
       <c r="E745" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="F745" t="n">
+        <v>237.29</v>
+      </c>
+      <c r="G745" t="n">
         <v>280</v>
-      </c>
-      <c r="G745" t="n">
-        <v>330.4</v>
       </c>
       <c r="H745">
         <f>הגדרות!B6</f>
@@ -37906,14 +37906,14 @@
       </c>
       <c r="E746" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="F746" t="n">
+        <v>237.29</v>
+      </c>
+      <c r="G746" t="n">
         <v>280</v>
-      </c>
-      <c r="G746" t="n">
-        <v>330.4</v>
       </c>
       <c r="H746">
         <f>הגדרות!B6</f>
@@ -37954,14 +37954,14 @@
       </c>
       <c r="E747" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="F747" t="n">
+        <v>237.29</v>
+      </c>
+      <c r="G747" t="n">
         <v>280</v>
-      </c>
-      <c r="G747" t="n">
-        <v>330.4</v>
       </c>
       <c r="H747">
         <f>הגדרות!B6</f>
@@ -38002,14 +38002,14 @@
       </c>
       <c r="E748" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="F748" t="n">
+        <v>237.29</v>
+      </c>
+      <c r="G748" t="n">
         <v>280</v>
-      </c>
-      <c r="G748" t="n">
-        <v>330.4</v>
       </c>
       <c r="H748">
         <f>הגדרות!B6</f>
@@ -38050,14 +38050,14 @@
       </c>
       <c r="E749" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="F749" t="n">
+        <v>237.29</v>
+      </c>
+      <c r="G749" t="n">
         <v>280</v>
-      </c>
-      <c r="G749" t="n">
-        <v>330.4</v>
       </c>
       <c r="H749">
         <f>הגדרות!B6</f>
@@ -38098,14 +38098,14 @@
       </c>
       <c r="E750" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="F750" t="n">
+        <v>237.29</v>
+      </c>
+      <c r="G750" t="n">
         <v>280</v>
-      </c>
-      <c r="G750" t="n">
-        <v>330.4</v>
       </c>
       <c r="H750">
         <f>הגדרות!B6</f>
@@ -38146,14 +38146,14 @@
       </c>
       <c r="E751" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="F751" t="n">
+        <v>237.29</v>
+      </c>
+      <c r="G751" t="n">
         <v>280</v>
-      </c>
-      <c r="G751" t="n">
-        <v>330.4</v>
       </c>
       <c r="H751">
         <f>הגדרות!B6</f>
@@ -38194,14 +38194,14 @@
       </c>
       <c r="E752" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="F752" t="n">
+        <v>237.29</v>
+      </c>
+      <c r="G752" t="n">
         <v>280</v>
-      </c>
-      <c r="G752" t="n">
-        <v>330.4</v>
       </c>
       <c r="H752">
         <f>הגדרות!B6</f>
@@ -38242,14 +38242,14 @@
       </c>
       <c r="E753" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="F753" t="n">
+        <v>237.29</v>
+      </c>
+      <c r="G753" t="n">
         <v>280</v>
-      </c>
-      <c r="G753" t="n">
-        <v>330.4</v>
       </c>
       <c r="H753">
         <f>הגדרות!B6</f>
@@ -38290,14 +38290,14 @@
       </c>
       <c r="E754" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="F754" t="n">
+        <v>169.49</v>
+      </c>
+      <c r="G754" t="n">
         <v>200</v>
-      </c>
-      <c r="G754" t="n">
-        <v>236</v>
       </c>
       <c r="H754">
         <f>הגדרות!B6</f>
@@ -38338,14 +38338,14 @@
       </c>
       <c r="E755" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="F755" t="n">
+        <v>169.49</v>
+      </c>
+      <c r="G755" t="n">
         <v>200</v>
-      </c>
-      <c r="G755" t="n">
-        <v>236</v>
       </c>
       <c r="H755">
         <f>הגדרות!B6</f>
@@ -38386,14 +38386,14 @@
       </c>
       <c r="E756" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="F756" t="n">
+        <v>169.49</v>
+      </c>
+      <c r="G756" t="n">
         <v>200</v>
-      </c>
-      <c r="G756" t="n">
-        <v>236</v>
       </c>
       <c r="H756">
         <f>הגדרות!B6</f>
@@ -38434,14 +38434,14 @@
       </c>
       <c r="E757" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="F757" t="n">
+        <v>169.49</v>
+      </c>
+      <c r="G757" t="n">
         <v>200</v>
-      </c>
-      <c r="G757" t="n">
-        <v>236</v>
       </c>
       <c r="H757">
         <f>הגדרות!B6</f>
@@ -38482,14 +38482,14 @@
       </c>
       <c r="E758" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="F758" t="n">
+        <v>169.49</v>
+      </c>
+      <c r="G758" t="n">
         <v>200</v>
-      </c>
-      <c r="G758" t="n">
-        <v>236</v>
       </c>
       <c r="H758">
         <f>הגדרות!B6</f>
@@ -38530,14 +38530,14 @@
       </c>
       <c r="E759" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="F759" t="n">
+        <v>169.49</v>
+      </c>
+      <c r="G759" t="n">
         <v>200</v>
-      </c>
-      <c r="G759" t="n">
-        <v>236</v>
       </c>
       <c r="H759">
         <f>הגדרות!B6</f>
@@ -38578,14 +38578,14 @@
       </c>
       <c r="E760" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="F760" t="n">
+        <v>169.49</v>
+      </c>
+      <c r="G760" t="n">
         <v>200</v>
-      </c>
-      <c r="G760" t="n">
-        <v>236</v>
       </c>
       <c r="H760">
         <f>הגדרות!B6</f>
@@ -38626,14 +38626,14 @@
       </c>
       <c r="E761" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="F761" t="n">
+        <v>169.49</v>
+      </c>
+      <c r="G761" t="n">
         <v>200</v>
-      </c>
-      <c r="G761" t="n">
-        <v>236</v>
       </c>
       <c r="H761">
         <f>הגדרות!B6</f>
@@ -38674,14 +38674,14 @@
       </c>
       <c r="E762" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="F762" t="n">
+        <v>220.34</v>
+      </c>
+      <c r="G762" t="n">
         <v>260</v>
-      </c>
-      <c r="G762" t="n">
-        <v>306.8</v>
       </c>
       <c r="H762">
         <f>הגדרות!B6</f>
@@ -38722,14 +38722,14 @@
       </c>
       <c r="E763" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="F763" t="n">
+        <v>169.49</v>
+      </c>
+      <c r="G763" t="n">
         <v>200</v>
-      </c>
-      <c r="G763" t="n">
-        <v>236</v>
       </c>
       <c r="H763">
         <f>הגדרות!B6</f>
@@ -38770,14 +38770,14 @@
       </c>
       <c r="E764" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="F764" t="n">
+        <v>169.49</v>
+      </c>
+      <c r="G764" t="n">
         <v>200</v>
-      </c>
-      <c r="G764" t="n">
-        <v>236</v>
       </c>
       <c r="H764">
         <f>הגדרות!B6</f>
@@ -38818,14 +38818,14 @@
       </c>
       <c r="E765" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="F765" t="n">
+        <v>220.34</v>
+      </c>
+      <c r="G765" t="n">
         <v>260</v>
-      </c>
-      <c r="G765" t="n">
-        <v>306.8</v>
       </c>
       <c r="H765">
         <f>הגדרות!B6</f>
@@ -38866,14 +38866,14 @@
       </c>
       <c r="E766" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="F766" t="n">
+        <v>220.34</v>
+      </c>
+      <c r="G766" t="n">
         <v>260</v>
-      </c>
-      <c r="G766" t="n">
-        <v>306.8</v>
       </c>
       <c r="H766">
         <f>הגדרות!B6</f>
@@ -38914,14 +38914,14 @@
       </c>
       <c r="E767" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="F767" t="n">
+        <v>169.49</v>
+      </c>
+      <c r="G767" t="n">
         <v>200</v>
-      </c>
-      <c r="G767" t="n">
-        <v>236</v>
       </c>
       <c r="H767">
         <f>הגדרות!B6</f>
@@ -38962,14 +38962,14 @@
       </c>
       <c r="E768" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="F768" t="n">
+        <v>169.49</v>
+      </c>
+      <c r="G768" t="n">
         <v>200</v>
-      </c>
-      <c r="G768" t="n">
-        <v>236</v>
       </c>
       <c r="H768">
         <f>הגדרות!B6</f>
@@ -39010,14 +39010,14 @@
       </c>
       <c r="E769" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="F769" t="n">
+        <v>169.49</v>
+      </c>
+      <c r="G769" t="n">
         <v>200</v>
-      </c>
-      <c r="G769" t="n">
-        <v>236</v>
       </c>
       <c r="H769">
         <f>הגדרות!B6</f>
@@ -39058,14 +39058,14 @@
       </c>
       <c r="E770" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="F770" t="n">
+        <v>169.49</v>
+      </c>
+      <c r="G770" t="n">
         <v>200</v>
-      </c>
-      <c r="G770" t="n">
-        <v>236</v>
       </c>
       <c r="H770">
         <f>הגדרות!B6</f>
@@ -39106,14 +39106,14 @@
       </c>
       <c r="E771" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="F771" t="n">
+        <v>220.34</v>
+      </c>
+      <c r="G771" t="n">
         <v>260</v>
-      </c>
-      <c r="G771" t="n">
-        <v>306.8</v>
       </c>
       <c r="H771">
         <f>הגדרות!B6</f>
@@ -39154,14 +39154,14 @@
       </c>
       <c r="E772" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="F772" t="n">
+        <v>169.49</v>
+      </c>
+      <c r="G772" t="n">
         <v>200</v>
-      </c>
-      <c r="G772" t="n">
-        <v>236</v>
       </c>
       <c r="H772">
         <f>הגדרות!B6</f>
@@ -39202,14 +39202,14 @@
       </c>
       <c r="E773" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="F773" t="n">
+        <v>169.49</v>
+      </c>
+      <c r="G773" t="n">
         <v>200</v>
-      </c>
-      <c r="G773" t="n">
-        <v>236</v>
       </c>
       <c r="H773">
         <f>הגדרות!B6</f>
@@ -39250,14 +39250,14 @@
       </c>
       <c r="E774" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="F774" t="n">
+        <v>169.49</v>
+      </c>
+      <c r="G774" t="n">
         <v>200</v>
-      </c>
-      <c r="G774" t="n">
-        <v>236</v>
       </c>
       <c r="H774">
         <f>הגדרות!B6</f>
@@ -39298,14 +39298,14 @@
       </c>
       <c r="E775" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="F775" t="n">
+        <v>169.49</v>
+      </c>
+      <c r="G775" t="n">
         <v>200</v>
-      </c>
-      <c r="G775" t="n">
-        <v>236</v>
       </c>
       <c r="H775">
         <f>הגדרות!B6</f>
@@ -39346,14 +39346,14 @@
       </c>
       <c r="E776" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="F776" t="n">
+        <v>169.49</v>
+      </c>
+      <c r="G776" t="n">
         <v>200</v>
-      </c>
-      <c r="G776" t="n">
-        <v>236</v>
       </c>
       <c r="H776">
         <f>הגדרות!B6</f>
@@ -39394,14 +39394,14 @@
       </c>
       <c r="E777" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="F777" t="n">
+        <v>169.49</v>
+      </c>
+      <c r="G777" t="n">
         <v>200</v>
-      </c>
-      <c r="G777" t="n">
-        <v>236</v>
       </c>
       <c r="H777">
         <f>הגדרות!B6</f>
@@ -39442,14 +39442,14 @@
       </c>
       <c r="E778" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="F778" t="n">
+        <v>169.49</v>
+      </c>
+      <c r="G778" t="n">
         <v>200</v>
-      </c>
-      <c r="G778" t="n">
-        <v>236</v>
       </c>
       <c r="H778">
         <f>הגדרות!B6</f>
@@ -39490,14 +39490,14 @@
       </c>
       <c r="E779" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="F779" t="n">
+        <v>169.49</v>
+      </c>
+      <c r="G779" t="n">
         <v>200</v>
-      </c>
-      <c r="G779" t="n">
-        <v>236</v>
       </c>
       <c r="H779">
         <f>הגדרות!B6</f>
@@ -39538,14 +39538,14 @@
       </c>
       <c r="E780" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="F780" t="n">
+        <v>220.34</v>
+      </c>
+      <c r="G780" t="n">
         <v>260</v>
-      </c>
-      <c r="G780" t="n">
-        <v>306.8</v>
       </c>
       <c r="H780">
         <f>הגדרות!B6</f>
@@ -39586,14 +39586,14 @@
       </c>
       <c r="E781" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="F781" t="n">
+        <v>169.49</v>
+      </c>
+      <c r="G781" t="n">
         <v>200</v>
-      </c>
-      <c r="G781" t="n">
-        <v>236</v>
       </c>
       <c r="H781">
         <f>הגדרות!B6</f>
@@ -39634,14 +39634,14 @@
       </c>
       <c r="E782" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="F782" t="n">
+        <v>159.32</v>
+      </c>
+      <c r="G782" t="n">
         <v>188</v>
-      </c>
-      <c r="G782" t="n">
-        <v>221.84</v>
       </c>
       <c r="H782">
         <f>הגדרות!B6</f>
@@ -39682,14 +39682,14 @@
       </c>
       <c r="E783" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="F783" t="n">
+        <v>159.32</v>
+      </c>
+      <c r="G783" t="n">
         <v>188</v>
-      </c>
-      <c r="G783" t="n">
-        <v>221.84</v>
       </c>
       <c r="H783">
         <f>הגדרות!B6</f>
@@ -39730,14 +39730,14 @@
       </c>
       <c r="E784" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="F784" t="n">
+        <v>597.46</v>
+      </c>
+      <c r="G784" t="n">
         <v>705</v>
-      </c>
-      <c r="G784" t="n">
-        <v>831.9</v>
       </c>
       <c r="H784">
         <f>הגדרות!B6</f>
@@ -39778,14 +39778,14 @@
       </c>
       <c r="E785" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="F785" t="n">
+        <v>364.41</v>
+      </c>
+      <c r="G785" t="n">
         <v>430</v>
-      </c>
-      <c r="G785" t="n">
-        <v>507.4</v>
       </c>
       <c r="H785">
         <f>הגדרות!B6</f>
@@ -39826,14 +39826,14 @@
       </c>
       <c r="E786" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="F786" t="n">
+        <v>402.54</v>
+      </c>
+      <c r="G786" t="n">
         <v>475</v>
-      </c>
-      <c r="G786" t="n">
-        <v>560.5</v>
       </c>
       <c r="H786">
         <f>הגדרות!B6</f>
@@ -39874,14 +39874,14 @@
       </c>
       <c r="E787" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="F787" t="n">
+        <v>372.88</v>
+      </c>
+      <c r="G787" t="n">
         <v>440</v>
-      </c>
-      <c r="G787" t="n">
-        <v>519.2</v>
       </c>
       <c r="H787">
         <f>הגדרות!B6</f>
@@ -39922,14 +39922,14 @@
       </c>
       <c r="E788" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="F788" t="n">
+        <v>559.3200000000001</v>
+      </c>
+      <c r="G788" t="n">
         <v>660</v>
-      </c>
-      <c r="G788" t="n">
-        <v>778.8</v>
       </c>
       <c r="H788">
         <f>הגדרות!B6</f>
@@ -39970,14 +39970,14 @@
       </c>
       <c r="E789" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="F789" t="n">
+        <v>364.41</v>
+      </c>
+      <c r="G789" t="n">
         <v>430</v>
-      </c>
-      <c r="G789" t="n">
-        <v>507.4</v>
       </c>
       <c r="H789">
         <f>הגדרות!B6</f>
@@ -40018,14 +40018,14 @@
       </c>
       <c r="E790" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="F790" t="n">
+        <v>652.54</v>
+      </c>
+      <c r="G790" t="n">
         <v>770</v>
-      </c>
-      <c r="G790" t="n">
-        <v>908.6</v>
       </c>
       <c r="H790">
         <f>הגדרות!B6</f>
@@ -40045,6 +40045,102 @@
       </c>
       <c r="L790">
         <f>I790*(1+J790/100)+K790</f>
+        <v/>
+      </c>
+    </row>
+    <row r="791">
+      <c r="A791" t="inlineStr">
+        <is>
+          <t>קרניאלי</t>
+        </is>
+      </c>
+      <c r="B791" t="inlineStr">
+        <is>
+          <t>Avian DNA Sexing — בדיקת זוויג לציפורים</t>
+        </is>
+      </c>
+      <c r="C791" t="inlineStr">
+        <is>
+          <t>ציפורים</t>
+        </is>
+      </c>
+      <c r="E791" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="F791" t="n">
+        <v>59.32</v>
+      </c>
+      <c r="G791" t="n">
+        <v>70</v>
+      </c>
+      <c r="H791">
+        <f>הגדרות!B6</f>
+        <v/>
+      </c>
+      <c r="I791">
+        <f>F791*(1-H791/100)*1.18</f>
+        <v/>
+      </c>
+      <c r="J791">
+        <f>הגדרות!C6</f>
+        <v/>
+      </c>
+      <c r="K791">
+        <f>הגדרות!D6</f>
+        <v/>
+      </c>
+      <c r="L791">
+        <f>I791*(1+J791/100)+K791</f>
+        <v/>
+      </c>
+    </row>
+    <row r="792">
+      <c r="A792" t="inlineStr">
+        <is>
+          <t>קרניאלי</t>
+        </is>
+      </c>
+      <c r="B792" t="inlineStr">
+        <is>
+          <t>Avian Pathogen Testing — בדיקת פתוגן בציפורים</t>
+        </is>
+      </c>
+      <c r="C792" t="inlineStr">
+        <is>
+          <t>ציפורים</t>
+        </is>
+      </c>
+      <c r="E792" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="F792" t="n">
+        <v>93.22</v>
+      </c>
+      <c r="G792" t="n">
+        <v>110</v>
+      </c>
+      <c r="H792">
+        <f>הגדרות!B6</f>
+        <v/>
+      </c>
+      <c r="I792">
+        <f>F792*(1-H792/100)*1.18</f>
+        <v/>
+      </c>
+      <c r="J792">
+        <f>הגדרות!C6</f>
+        <v/>
+      </c>
+      <c r="K792">
+        <f>הגדרות!D6</f>
+        <v/>
+      </c>
+      <c r="L792">
+        <f>I792*(1+J792/100)+K792</f>
         <v/>
       </c>
     </row>
